--- a/data/testcases.xlsx
+++ b/data/testcases.xlsx
@@ -433,11 +433,11 @@
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1118,7 +1118,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1132,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -1249,9 +1247,6 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1292,6 @@
           <t>launch</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1305,13 +1299,11 @@
           <t>TC_WIN</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>start_challenge</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1319,7 +1311,6 @@
           <t>TC_WIN</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>play_gpx</t>
@@ -1337,7 +1328,6 @@
           <t>TC_WIN</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>assert_visible</t>
@@ -1370,9 +1360,6 @@
           <t>0.85 (같은 흐름, 배속만 낮춤 → 느림)</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">

--- a/data/testcases.xlsx
+++ b/data/testcases.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -850,25 +850,21 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC4</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr"/>
+          <t>TC5</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>기록 탭 진입</t>
+        </is>
+      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>assert_visible</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>계속 진행</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>에뮬은 걸음센서 안내 팝업</t>
-        </is>
-      </c>
+          <t>launch</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -876,17 +872,17 @@
           <t>TC5</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>기록 탭 진입</t>
-        </is>
-      </c>
+      <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>launch</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
+          <t>tap_text</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
@@ -898,12 +894,12 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>tap_text</t>
+          <t>assert_visible</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>기록</t>
+          <t>월간</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -911,20 +907,20 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC5</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr"/>
+          <t>TC_WIN</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>대결 상대보다 빠름(승리)</t>
+        </is>
+      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>assert_visible</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>기록</t>
-        </is>
-      </c>
+          <t>launch</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -933,18 +929,18 @@
           <t>TC_WIN</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>대결 상대보다 빠름(승리)</t>
-        </is>
-      </c>
+      <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>launch</t>
+          <t>start_challenge</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>챌린지→도전하기→가이드→원형석 선택→시작하기</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -955,13 +951,17 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>start_challenge</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>play_gpx</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>챌린지→도전하기→가이드→원형석 선택→시작하기</t>
+          <t>1.15배속 재생 → 원형석보다 빠른 페이스</t>
         </is>
       </c>
     </row>
@@ -974,42 +974,38 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>play_gpx</t>
+          <t>assert_winner</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>63run</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1.15배속 재생 → 원형석보다 빠른 페이스</t>
+          <t>승리 결과 화면</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC_WIN</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr"/>
+          <t>TC_LOSE</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>대결 상대보다 느림(패배)</t>
+        </is>
+      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>assert_visible</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>WINNER</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>승리 결과 화면</t>
-        </is>
-      </c>
+          <t>launch</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1017,14 +1013,10 @@
           <t>TC_LOSE</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>대결 상대보다 느림(패배)</t>
-        </is>
-      </c>
+      <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>launch</t>
+          <t>start_challenge</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1039,11 +1031,19 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>start_challenge</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>play_gpx</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>0.85배속 재생 → 원형석보다 느린 페이스</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1054,38 +1054,15 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>play_gpx</t>
+          <t>assert_winner</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>원형석</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>0.85배속 재생 → 원형석보다 느린 페이스</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TC_LOSE</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>assert_visible</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>LOSE</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>패배 결과 화면</t>
         </is>
